--- a/artfynd/A 3368-2023 artfynd.xlsx
+++ b/artfynd/A 3368-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3368-2023 artfynd.xlsx
+++ b/artfynd/A 3368-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2198,6 +2198,312 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124784899</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91919</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kvarnträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>858422</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7323549</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124784896</v>
+      </c>
+      <c r="B15" t="n">
+        <v>86495</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3690</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vaxspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius pinophilus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kvarnträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>858414</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7323543</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124784895</v>
+      </c>
+      <c r="B16" t="n">
+        <v>86495</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3690</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vaxspindling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cortinarius pinophilus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kvarnträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>858423</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7323567</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3368-2023 artfynd.xlsx
+++ b/artfynd/A 3368-2023 artfynd.xlsx
@@ -2200,10 +2200,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124784899</v>
+        <v>124784895</v>
       </c>
       <c r="B14" t="n">
-        <v>91919</v>
+        <v>86495</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2216,21 +2216,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>858422</v>
+        <v>858423</v>
       </c>
       <c r="R14" t="n">
-        <v>7323549</v>
+        <v>7323567</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124784895</v>
+        <v>124784899</v>
       </c>
       <c r="B16" t="n">
-        <v>86495</v>
+        <v>91919</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3690</v>
+        <v>4745</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>858423</v>
+        <v>858422</v>
       </c>
       <c r="R16" t="n">
-        <v>7323567</v>
+        <v>7323549</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 3368-2023 artfynd.xlsx
+++ b/artfynd/A 3368-2023 artfynd.xlsx
@@ -2200,7 +2200,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124784895</v>
+        <v>124784896</v>
       </c>
       <c r="B14" t="n">
         <v>86495</v>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>858423</v>
+        <v>858414</v>
       </c>
       <c r="R14" t="n">
-        <v>7323567</v>
+        <v>7323543</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124784896</v>
+        <v>124784895</v>
       </c>
       <c r="B15" t="n">
         <v>86495</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>858414</v>
+        <v>858423</v>
       </c>
       <c r="R15" t="n">
-        <v>7323543</v>
+        <v>7323567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 3368-2023 artfynd.xlsx
+++ b/artfynd/A 3368-2023 artfynd.xlsx
@@ -2200,10 +2200,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124784896</v>
+        <v>124784899</v>
       </c>
       <c r="B14" t="n">
-        <v>86495</v>
+        <v>91919</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2216,21 +2216,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3690</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>858414</v>
+        <v>858422</v>
       </c>
       <c r="R14" t="n">
-        <v>7323543</v>
+        <v>7323549</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124784895</v>
+        <v>124784896</v>
       </c>
       <c r="B15" t="n">
         <v>86495</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>858423</v>
+        <v>858414</v>
       </c>
       <c r="R15" t="n">
-        <v>7323567</v>
+        <v>7323543</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124784899</v>
+        <v>124784895</v>
       </c>
       <c r="B16" t="n">
-        <v>91919</v>
+        <v>86495</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>858422</v>
+        <v>858423</v>
       </c>
       <c r="R16" t="n">
-        <v>7323549</v>
+        <v>7323567</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 3368-2023 artfynd.xlsx
+++ b/artfynd/A 3368-2023 artfynd.xlsx
@@ -2302,7 +2302,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124784896</v>
+        <v>124784895</v>
       </c>
       <c r="B15" t="n">
         <v>86495</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>858414</v>
+        <v>858423</v>
       </c>
       <c r="R15" t="n">
-        <v>7323543</v>
+        <v>7323567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124784895</v>
+        <v>124784896</v>
       </c>
       <c r="B16" t="n">
         <v>86495</v>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>858423</v>
+        <v>858414</v>
       </c>
       <c r="R16" t="n">
-        <v>7323567</v>
+        <v>7323543</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 3368-2023 artfynd.xlsx
+++ b/artfynd/A 3368-2023 artfynd.xlsx
@@ -2200,10 +2200,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124784899</v>
+        <v>124784896</v>
       </c>
       <c r="B14" t="n">
-        <v>91919</v>
+        <v>86495</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2216,21 +2216,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>858422</v>
+        <v>858414</v>
       </c>
       <c r="R14" t="n">
-        <v>7323549</v>
+        <v>7323543</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124784895</v>
+        <v>124784899</v>
       </c>
       <c r="B15" t="n">
-        <v>86495</v>
+        <v>91919</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2318,21 +2318,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3690</v>
+        <v>4745</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>858423</v>
+        <v>858422</v>
       </c>
       <c r="R15" t="n">
-        <v>7323567</v>
+        <v>7323549</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124784896</v>
+        <v>124784895</v>
       </c>
       <c r="B16" t="n">
         <v>86495</v>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>858414</v>
+        <v>858423</v>
       </c>
       <c r="R16" t="n">
-        <v>7323543</v>
+        <v>7323567</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 3368-2023 artfynd.xlsx
+++ b/artfynd/A 3368-2023 artfynd.xlsx
@@ -2302,10 +2302,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124784899</v>
+        <v>124784895</v>
       </c>
       <c r="B15" t="n">
-        <v>91919</v>
+        <v>86495</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2318,21 +2318,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>858422</v>
+        <v>858423</v>
       </c>
       <c r="R15" t="n">
-        <v>7323549</v>
+        <v>7323567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124784895</v>
+        <v>124784899</v>
       </c>
       <c r="B16" t="n">
-        <v>86495</v>
+        <v>91919</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3690</v>
+        <v>4745</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>858423</v>
+        <v>858422</v>
       </c>
       <c r="R16" t="n">
-        <v>7323567</v>
+        <v>7323549</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 3368-2023 artfynd.xlsx
+++ b/artfynd/A 3368-2023 artfynd.xlsx
@@ -2302,10 +2302,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124784895</v>
+        <v>124784899</v>
       </c>
       <c r="B15" t="n">
-        <v>86495</v>
+        <v>91919</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2318,21 +2318,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3690</v>
+        <v>4745</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>858423</v>
+        <v>858422</v>
       </c>
       <c r="R15" t="n">
-        <v>7323567</v>
+        <v>7323549</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124784899</v>
+        <v>124784895</v>
       </c>
       <c r="B16" t="n">
-        <v>91919</v>
+        <v>86495</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>858422</v>
+        <v>858423</v>
       </c>
       <c r="R16" t="n">
-        <v>7323549</v>
+        <v>7323567</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 3368-2023 artfynd.xlsx
+++ b/artfynd/A 3368-2023 artfynd.xlsx
@@ -2200,10 +2200,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124784896</v>
+        <v>124784899</v>
       </c>
       <c r="B14" t="n">
-        <v>86495</v>
+        <v>91919</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2216,21 +2216,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3690</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>858414</v>
+        <v>858422</v>
       </c>
       <c r="R14" t="n">
-        <v>7323543</v>
+        <v>7323549</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124784899</v>
+        <v>124784895</v>
       </c>
       <c r="B15" t="n">
-        <v>91919</v>
+        <v>86495</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2318,21 +2318,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>858422</v>
+        <v>858423</v>
       </c>
       <c r="R15" t="n">
-        <v>7323549</v>
+        <v>7323567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124784895</v>
+        <v>124784896</v>
       </c>
       <c r="B16" t="n">
         <v>86495</v>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>858423</v>
+        <v>858414</v>
       </c>
       <c r="R16" t="n">
-        <v>7323567</v>
+        <v>7323543</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 3368-2023 artfynd.xlsx
+++ b/artfynd/A 3368-2023 artfynd.xlsx
@@ -2302,7 +2302,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124784895</v>
+        <v>124784896</v>
       </c>
       <c r="B15" t="n">
         <v>86495</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>858423</v>
+        <v>858414</v>
       </c>
       <c r="R15" t="n">
-        <v>7323567</v>
+        <v>7323543</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124784896</v>
+        <v>124784895</v>
       </c>
       <c r="B16" t="n">
         <v>86495</v>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>858414</v>
+        <v>858423</v>
       </c>
       <c r="R16" t="n">
-        <v>7323543</v>
+        <v>7323567</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 3368-2023 artfynd.xlsx
+++ b/artfynd/A 3368-2023 artfynd.xlsx
@@ -2200,10 +2200,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124784899</v>
+        <v>124784896</v>
       </c>
       <c r="B14" t="n">
-        <v>91919</v>
+        <v>86495</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2216,21 +2216,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>858422</v>
+        <v>858414</v>
       </c>
       <c r="R14" t="n">
-        <v>7323549</v>
+        <v>7323543</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124784896</v>
+        <v>124784895</v>
       </c>
       <c r="B15" t="n">
         <v>86495</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>858414</v>
+        <v>858423</v>
       </c>
       <c r="R15" t="n">
-        <v>7323543</v>
+        <v>7323567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124784895</v>
+        <v>124784899</v>
       </c>
       <c r="B16" t="n">
-        <v>86495</v>
+        <v>91919</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3690</v>
+        <v>4745</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>858423</v>
+        <v>858422</v>
       </c>
       <c r="R16" t="n">
-        <v>7323567</v>
+        <v>7323549</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 3368-2023 artfynd.xlsx
+++ b/artfynd/A 3368-2023 artfynd.xlsx
@@ -2200,10 +2200,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124784896</v>
+        <v>124784895</v>
       </c>
       <c r="B14" t="n">
-        <v>86495</v>
+        <v>86643</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>858414</v>
+        <v>858423</v>
       </c>
       <c r="R14" t="n">
-        <v>7323543</v>
+        <v>7323567</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124784895</v>
+        <v>124784896</v>
       </c>
       <c r="B15" t="n">
-        <v>86495</v>
+        <v>86643</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>858423</v>
+        <v>858414</v>
       </c>
       <c r="R15" t="n">
-        <v>7323567</v>
+        <v>7323543</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2407,7 +2407,7 @@
         <v>124784899</v>
       </c>
       <c r="B16" t="n">
-        <v>91919</v>
+        <v>92070</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 3368-2023 artfynd.xlsx
+++ b/artfynd/A 3368-2023 artfynd.xlsx
@@ -2200,7 +2200,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124784895</v>
+        <v>124784896</v>
       </c>
       <c r="B14" t="n">
         <v>86643</v>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>858423</v>
+        <v>858414</v>
       </c>
       <c r="R14" t="n">
-        <v>7323567</v>
+        <v>7323543</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124784896</v>
+        <v>124784895</v>
       </c>
       <c r="B15" t="n">
         <v>86643</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>858414</v>
+        <v>858423</v>
       </c>
       <c r="R15" t="n">
-        <v>7323543</v>
+        <v>7323567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
